--- a/output/pdf_financials_xlsx/RAMP.xlsx
+++ b/output/pdf_financials_xlsx/RAMP.xlsx
@@ -2813,22 +2813,22 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.02562</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.027597</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.027597</v>
       </c>
       <c r="E92" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.188839</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.204575</v>
       </c>
     </row>
     <row r="93">
@@ -4674,7 +4674,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -5002,7 +5006,11 @@
           <t>Reserves (Note 4)</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -5324,7 +5332,11 @@
           <t>Share-based payment reserve (note 5)</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E30" s="5" t="n">
         <v>0.01281</v>
       </c>

--- a/output/pdf_financials_xlsx/RAMP.xlsx
+++ b/output/pdf_financials_xlsx/RAMP.xlsx
@@ -711,10 +711,10 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.016218</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.106898</v>
       </c>
     </row>
     <row r="13">
@@ -1112,10 +1112,10 @@
         <v>-0.22425</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.05185</v>
+        <v>0.035632</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.788388</v>
+        <v>0.68149</v>
       </c>
     </row>
     <row r="28">
@@ -1162,10 +1162,10 @@
         <v>-0.22425</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.05185</v>
+        <v>0.035632</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.788388</v>
+        <v>0.68149</v>
       </c>
     </row>
     <row r="30">
@@ -1281,16 +1281,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.119735</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.185974</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.09468799999999999</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.086866</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>0.194777</v>
@@ -1331,16 +1331,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.119735</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.185974</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.09468799999999999</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.086866</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>0.194777</v>
@@ -1631,16 +1631,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.134735</v>
+        <v>0.015</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.185974</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.095598</v>
+        <v>0.00091</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.138419</v>
+        <v>0.051553</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0.159071</v>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E25" s="5" t="n">
@@ -9502,7 +9502,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">

--- a/output/pdf_financials_xlsx/RAMP.xlsx
+++ b/output/pdf_financials_xlsx/RAMP.xlsx
@@ -583,13 +583,13 @@
         <v>9.2e-05</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.147603</v>
+        <v>0.150652</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.195371</v>
+        <v>0.204801</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.293803</v>
+        <v>0.303359</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>0</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>-0.021599</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0</v>
+        <v>-0.057326</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0</v>
+        <v>-0.080707</v>
       </c>
     </row>
     <row r="102">
@@ -3166,13 +3166,13 @@
         <v>-0.09128600000000001</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0.01623</v>
+        <v>-0.005369</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0.295371</v>
+        <v>0.238045</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>-0.002803</v>
+        <v>-0.08351</v>
       </c>
     </row>
     <row r="107">
@@ -5882,7 +5882,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -6022,7 +6026,11 @@
           <t>GST recoverable</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>
@@ -6432,7 +6440,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
@@ -9044,7 +9056,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
           <t>-</t>
